--- a/knowledge/AgriAI_knowledge_base.xlsx
+++ b/knowledge/AgriAI_knowledge_base.xlsx
@@ -17,11 +17,11 @@
     <sheet name="Lists" sheetId="7" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Advisor questions'!$A$1:$E$9</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Facts!$A$1:$R$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Season stages'!$A$1:$L$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Sources!$A$1:$N$23</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Topics!$A$1:$H$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Advisor questions'!$A$1:$E$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Facts!$A$1:$S$32</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Season stages'!$A$1:$L$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Sources!$A$1:$N$37</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Topics!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -82,7 +82,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Which picture the page draws for this topic.</t>
+          <t xml:space="preserve">Optional. A safety warning shown in a red box at the top of the topic. Leave blank for most topics.</t>
         </r>
       </text>
     </comment>
@@ -94,7 +94,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">yes = What to do is numbered and must be done in order. no = independent actions.</t>
+          <t xml:space="preserve">Which picture the page draws for this topic.</t>
         </r>
       </text>
     </comment>
@@ -106,7 +106,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Automatic. Facts in this topic with status live.</t>
+          <t xml:space="preserve">yes = What to do is numbered and must be done in order. no = independent actions.</t>
         </r>
       </text>
     </comment>
@@ -118,11 +118,23 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Automatic. Facts in this topic with status live.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Automatic. All facts in this topic.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +200,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">The step the farmer does, shown in What to do and My season. Under 10 words, starts with a verb.</t>
+          <t xml:space="preserve">Optional. Label above the step, e.g. 'At harvest'. If blank the app shows First, Then, Finally.</t>
         </r>
       </text>
     </comment>
@@ -200,7 +212,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Icon next to the step.</t>
+          <t xml:space="preserve">The step the farmer does, shown in What to do and My season. Under 10 words, starts with a verb.</t>
         </r>
       </text>
     </comment>
@@ -212,7 +224,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Headline of the Did you know card. Under 8 words.</t>
+          <t xml:space="preserve">Icon next to the step.</t>
         </r>
       </text>
     </comment>
@@ -224,7 +236,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Plain English, under 25 words, one idea. Shown when the farmer taps Why?, and given to the advisor.</t>
+          <t xml:space="preserve">Headline of the Did you know card. Under 8 words.</t>
         </r>
       </text>
     </comment>
@@ -236,7 +248,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Optional. A surprising one-liner for the Did you know card. If blank the card uses farmer_summary.</t>
+          <t xml:space="preserve">Plain English, under 25 words, one idea. Shown when the farmer taps Why?, and given to the advisor.</t>
         </r>
       </text>
     </comment>
@@ -248,7 +260,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Optional. A number with its unit and region, e.g. '2 bags per acre, Central region'.</t>
+          <t xml:space="preserve">Optional. A surprising one-liner for the Did you know card. If blank the card uses farmer_summary.</t>
         </r>
       </text>
     </comment>
@@ -260,7 +272,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Who should see it. 'all farms' for everyone.</t>
+          <t xml:space="preserve">Optional. A number with its unit and region, e.g. '2 bags per acre, Central region'.</t>
         </r>
       </text>
     </comment>
@@ -272,7 +284,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">draft = being written. checked = facts and sources verified. live = shown in the app. retired = no longer shown.</t>
+          <t xml:space="preserve">Who should see it. 'all farms' for everyone.</t>
         </r>
       </text>
     </comment>
@@ -284,7 +296,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Who is responsible for this row.</t>
+          <t xml:space="preserve">draft = being written. checked = facts and sources verified. live = shown in the app. retired = no longer shown.</t>
         </r>
       </text>
     </comment>
@@ -296,7 +308,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Date the content and sources were last verified.</t>
+          <t xml:space="preserve">Who is responsible for this row.</t>
         </r>
       </text>
     </comment>
@@ -308,7 +320,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">What evidence is missing. Not shown in the app.</t>
+          <t xml:space="preserve">Date the content and sources were last verified.</t>
         </r>
       </text>
     </comment>
@@ -320,7 +332,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Working notes. Not shown in the app.</t>
+          <t xml:space="preserve">What evidence is missing. Not shown in the app.</t>
         </r>
       </text>
     </comment>
@@ -332,7 +344,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Automatic. Number of rows on the Sources tab for this fact.</t>
+          <t xml:space="preserve">Working notes. Not shown in the app.</t>
         </r>
       </text>
     </comment>
@@ -344,11 +356,23 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Automatic. Number of rows on the Sources tab for this fact.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Automatic. Sources marked checked = yes.</t>
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -767,7 +791,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="516">
   <si>
     <t xml:space="preserve">AgriAI Malawi knowledge base</t>
   </si>
@@ -970,6 +994,9 @@
     <t xml:space="preserve">why</t>
   </si>
   <si>
+    <t xml:space="preserve">alert</t>
+  </si>
+  <si>
     <t xml:space="preserve">visual</t>
   </si>
   <si>
@@ -1054,12 +1081,27 @@
     <t xml:space="preserve">storage</t>
   </si>
   <si>
+    <t xml:space="preserve">Aflatoxin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mould on maize and groundnuts can make aflatoxin, a poison that harms the liver and children's growth. Good drying, sorting and storage keep it out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not eat, sell or feed animals mouldy grain. Soaking and fermenting do not remove the poison.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aflatoxin</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
     <t xml:space="preserve">step_order</t>
   </si>
   <si>
+    <t xml:space="preserve">phase</t>
+  </si>
+  <si>
     <t xml:space="preserve">action</t>
   </si>
   <si>
@@ -1237,9 +1279,6 @@
     <t xml:space="preserve">Don't replant seed saved from a hybrid crop</t>
   </si>
   <si>
-    <t xml:space="preserve">alert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Don't replant hybrid seed</t>
   </si>
   <si>
@@ -1462,6 +1501,174 @@
     <t xml:space="preserve">Storage losses with and without raised storage.</t>
   </si>
   <si>
+    <t xml:space="preserve">afla-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before flowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask about Aflasafe 2 to 3 weeks before flowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A good fungus that protects the crop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflasafe puts harmless fungi in the field that crowd out the ones that make aflatoxin. It is registered in Malawi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In trials in 11 Malawi districts, Aflasafe cut aflatoxin in maize by more than 80%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where farmers can buy Aflasafe in Malawi, price per acre, application rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At harvest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvest as soon as the cobs are dry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not leave dry maize in the field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobs left standing after they are dry pick up more mould and insects. Harvest when husks are dry like paper and cobs hang down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi evidence on aflatoxin increase with delayed harvest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry on a tarpaulin or mat, never on bare ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep cobs off the soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mould that makes aflatoxin lives in soil. Dry maize on a tarpaulin, mat or raised rack, never on bare ground.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In southern Malawi, farmers who dried maize on tarpaulins cut aflatoxin by about a fifth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort out mouldy, broken and discoloured grain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorting removes most of the poison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most aflatoxin sits in a few bad grains. Picking out mouldy, broken, shrivelled and discoloured grain removes much of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorting out bad grains alone can remove 40 to 80% of aflatoxin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before storing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry the grain to about 13% moisture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry enough to store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mould grows in damp grain. Store maize at about 13% moisture. Salt test: shake grain with dry salt in a jar for 2 to 3 minutes. If the salt does not stick, it is dry enough.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A jar of dry salt can tell you if maize is dry enough to store.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi recommended storage moisture and a validated salt test method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store in a sealed bag, off the floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sealed bags stop mould growing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hermetic bags such as PICS keep air out, so mould and weevils cannot grow. Keep bags off the floor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Kenya, maize in hermetic bags had about one third of the aflatoxin of normal bags after 8 months.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi trial of hermetic storage and aflatoxin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A hidden poison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxin is made by mould on maize and groundnuts. It causes liver cancer and is linked to stunting in young children.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 500 million of the world's poorest people eat aflatoxin in their staple food every day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soaking does not make it safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxin stays in maize through soaking and fermenting. Throw away mouldy grain instead of trying to clean it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In one study, aflatoxin was still there after maize was soaked and fermented for days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A source on whether cooking reduces aflatoxin (often said not to).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not safe for animals either</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxin in mouldy feed passes into cows' milk. Do not feed mouldy grain to animals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afla-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common in Malawi maize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxin is common in maize and groundnuts in Malawi, and it costs the country export income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In one study in southern Malawi, almost half of maize samples had more aflatoxin than the 20 ppb safety level.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi Bureau of Standards limit for aflatoxin in maize.</t>
+  </si>
+  <si>
     <t xml:space="preserve">source_id</t>
   </si>
   <si>
@@ -1756,6 +1963,195 @@
     <t xml:space="preserve">https://www.researchgate.net/publication/316112963_Field_efficacy_of_hermetic_and_other_maize_grain_storage_options_under_smallholder_farmer_management</t>
   </si>
   <si>
+    <t xml:space="preserve">src-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi registers Aflasafe, the cost-effective technology for aflatoxin management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.iita.org/news-item/malawi-registers-aflasafe-the-cost-effective-technology-for-aflatoxin-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflasafe MWMZ01 and MW02 registered for maize and groundnut; applied 2 to 3 weeks before flowering; trials in 11 districts cut aflatoxin by over 80%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGO or extension guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addressing aflatoxin contamination and improving food safety in Malawi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFPRI Malawi Strategy Support Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://massp.ifpri.info/2019/05/03/addressing-aflatoxin-contamination-and-improving-food-safety-in-malawi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Malawi-specific Aflasafe products were cleared in December 2018; good drying, harvest and storage practices also reduce aflatoxin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reducing post-harvest losses in maize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm Radio International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://scripts.farmradio.fm/?p=12229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvest when husks are dry like paper and cobs droop; separate damaged cobs right away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knowledge, attitude and practice of Malawian farmers on pre- and post-harvest crop management to mitigate aflatoxin contamination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toxins (Anitha et al.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mdpi.com/2072-6651/11/12/716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farmers who adopted drying on tarpaulins saw mean aflatoxin fall from 72 to 56 ppb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never dry maize on bare ground; use tarpaulins, mats or raised racks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farmers who adopted grading saw aflatoxin fall from 73 to 51 ppb; physical sorting alone cuts contamination by 40 to 80%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store at about 13.5% moisture or below; salt jar test: salt that does not stick after 2 to 3 minutes means under 15% moisture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affordable grain drying and storage technologies cut down aflatoxins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrilinks (CIMMYT, KALRO, Purdue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://agrilinks.org/post/affordable-grain-drying-and-storage-technologies-cut-down-aflatoxins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grain at 12 to 13% moisture kept better; grain at 14 to 15% degraded faster and was more prone to mycotoxins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After 8 months, maize in PICS hermetic bags had about one third of the aflatoxin of insecticide-treated woven bags (Kenya).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARC report urges action against widespread mycotoxin contamination in developing countries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Agency for Research on Cancer (WHO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.iarc.who.int/wp-content/uploads/2018/07/pr242_E.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxin is a cause of human liver cancer; about 500 million of the poorest people are exposed daily; mycotoxins likely contribute to stunting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persistence of aflatoxins during traditional steeping and fermentation of maize in Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIR Food Research Institute (Kpodo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://csirspace.foodresearchgh.org/handle/1/716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxins persisted through steeping and fermentation; 17 of 30 dough samples exceeded 30 ug/kg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to prevent aflatoxin in milk at farm level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KALRO Veterinary Research Institute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://navcdp.kalro.org/docs/tots/kscap/AFLATOXIN.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aflatoxin from mouldy feed carries over into milk; check feed and destroy spoiled feed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At baseline, 44.8% of maize samples from Blantyre, Chikwawa and Nsanje were above 20 ppb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The African Union estimates Malawi loses about US$88 million a year in exports due to aflatoxin in groundnuts and maize.</t>
+  </si>
+  <si>
     <t xml:space="preserve">stage_id</t>
   </si>
   <si>
@@ -1840,7 +2236,16 @@
     <t xml:space="preserve">Harvest when the cobs are dry</t>
   </si>
   <si>
-    <t xml:space="preserve">The husks turn brown and the cobs hang down.</t>
+    <t xml:space="preserve">The husks turn brown and the cobs hang down. Do not leave dry cobs in the field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort out mouldy and broken grain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouldy grain can carry aflatoxin. Do not eat, sell or feed it to animals.</t>
   </si>
   <si>
     <t xml:space="preserve">store</t>
@@ -1882,18 +2287,18 @@
     <t xml:space="preserve">How do I store maize safely?</t>
   </si>
   <si>
+    <t xml:space="preserve">How do I keep aflatoxin out of my maize?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is it safe to eat mouldy maize?</t>
+  </si>
+  <si>
     <t xml:space="preserve">yes_no</t>
   </si>
   <si>
     <t xml:space="preserve">icon</t>
   </si>
   <si>
-    <t xml:space="preserve">research study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malawi</t>
-  </si>
-  <si>
     <t xml:space="preserve">government guide</t>
   </si>
   <si>
@@ -1903,19 +2308,10 @@
     <t xml:space="preserve">maize only</t>
   </si>
   <si>
-    <t xml:space="preserve">NGO or extension guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sub-Saharan Africa</t>
-  </si>
-  <si>
     <t xml:space="preserve">uses fertilizer</t>
   </si>
   <si>
     <t xml:space="preserve">dataset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global</t>
   </si>
   <si>
     <t xml:space="preserve">no fertilizer</t>
@@ -2201,7 +2597,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2261,6 +2657,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9A4A06"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE0B2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2797,7 +3201,7 @@
       </c>
       <c r="B38" s="8" t="n">
         <f aca="false">COUNTA(Facts!A2:A300)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2805,7 +3209,7 @@
         <v>56</v>
       </c>
       <c r="B39" s="8" t="n">
-        <f aca="false">COUNTIF(Facts!K2:K300,"live")</f>
+        <f aca="false">COUNTIF(Facts!L2:L300,"live")</f>
         <v>0</v>
       </c>
     </row>
@@ -2814,7 +3218,7 @@
         <v>57</v>
       </c>
       <c r="B40" s="8" t="n">
-        <f aca="false">COUNTIF(Facts!R2:R300,"Yes")</f>
+        <f aca="false">COUNTIF(Facts!S2:S300,"Yes")</f>
         <v>0</v>
       </c>
     </row>
@@ -2823,7 +3227,7 @@
         <v>58</v>
       </c>
       <c r="B41" s="8" t="n">
-        <f aca="false">COUNTIFS(Facts!K2:K300,"live",Facts!Q2:Q300,0)</f>
+        <f aca="false">COUNTIFS(Facts!L2:L300,"live",Facts!R2:R300,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2832,7 +3236,7 @@
         <v>59</v>
       </c>
       <c r="B42" s="8" t="n">
-        <f aca="false">COUNTIFS(Facts!A2:A300,"&lt;&gt;",Facts!P2:P300,0)</f>
+        <f aca="false">COUNTIFS(Facts!A2:A300,"&lt;&gt;",Facts!Q2:Q300,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -2842,7 +3246,7 @@
       </c>
       <c r="B43" s="8" t="n">
         <f aca="false">COUNTA(Sources!A2:A300)</f>
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2888,16 +3292,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2910,212 +3315,251 @@
       <c r="C1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>71</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="13" t="s">
         <v>74</v>
       </c>
+      <c r="D2" s="13"/>
       <c r="E2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A2,Facts!$K:$K,"live")</f>
+      <c r="F2" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A2,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="H2" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A2)</f>
         <v>3</v>
       </c>
-      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="13" t="s">
         <v>78</v>
       </c>
+      <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A3,Facts!$K:$K,"live")</f>
+        <v>79</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A3,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="H3" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A3)</f>
         <v>3</v>
       </c>
-      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="13" t="s">
         <v>81</v>
       </c>
+      <c r="D4" s="13"/>
       <c r="E4" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A4,Facts!$K:$K,"live")</f>
+      <c r="F4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A4,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="H4" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A4)</f>
         <v>3</v>
       </c>
-      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="13" t="s">
         <v>85</v>
       </c>
+      <c r="D5" s="13"/>
       <c r="E5" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A5,Facts!$K:$K,"live")</f>
+        <v>86</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A5,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="H5" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A5)</f>
         <v>3</v>
       </c>
-      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="13" t="s">
         <v>88</v>
       </c>
+      <c r="D6" s="13"/>
       <c r="E6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A6,Facts!$K:$K,"live")</f>
+        <v>89</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A6,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="H6" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A6)</f>
         <v>3</v>
       </c>
-      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="13" t="s">
         <v>91</v>
       </c>
+      <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A7,Facts!$K:$K,"live")</f>
+        <v>92</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A7,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="H7" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A7)</f>
         <v>3</v>
       </c>
-      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="13" t="s">
         <v>94</v>
       </c>
+      <c r="D8" s="13"/>
       <c r="E8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <f aca="false">COUNTIFS(Facts!$B:$B,A8,Facts!$K:$K,"live")</f>
+        <v>95</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A8,Facts!$L:$L,"live")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="H8" s="14" t="n">
         <f aca="false">COUNTIF(Facts!$B:$B,A8)</f>
         <v>3</v>
       </c>
-      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <f aca="false">COUNTIFS(Facts!$B:$B,A9,Facts!$L:$L,"live")</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <f aca="false">COUNTIF(Facts!$B:$B,A9)</f>
+        <v>10</v>
+      </c>
+      <c r="I9" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:I9"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D300" type="list">
+    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E300" type="list">
       <formula1>Lists!$D$2:$D$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E300" type="list">
+    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F300" type="list">
       <formula1>Lists!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3137,1133 +3581,1654 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>113</v>
-      </c>
+      <c r="D2" s="13"/>
       <c r="E2" s="13" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="13"/>
+        <v>121</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="I2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J2" s="13"/>
       <c r="K2" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="13"/>
       <c r="M2" s="13"/>
-      <c r="N2" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="O2" s="13"/>
-      <c r="P2" s="14" t="n">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A2)</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="14" t="n">
+      <c r="R2" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A2,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R2" s="15" t="str">
-        <f aca="false">IF(AND(D2&lt;&gt;"",F2&lt;&gt;"",G2&lt;&gt;"",Q2&gt;=1),"Yes","Not yet")</f>
+      <c r="S2" s="15" t="str">
+        <f aca="false">IF(AND(E2&lt;&gt;"",G2&lt;&gt;"",H2&lt;&gt;"",R2&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>120</v>
-      </c>
+      <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" s="13" t="s">
+      <c r="L3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="13"/>
       <c r="M3" s="13"/>
-      <c r="N3" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="14" t="n">
+      <c r="N3" s="13"/>
+      <c r="O3" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A3)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="14" t="n">
+      <c r="R3" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A3,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R3" s="15" t="str">
-        <f aca="false">IF(AND(D3&lt;&gt;"",F3&lt;&gt;"",G3&lt;&gt;"",Q3&gt;=1),"Yes","Not yet")</f>
+      <c r="S3" s="15" t="str">
+        <f aca="false">IF(AND(E3&lt;&gt;"",G3&lt;&gt;"",H3&lt;&gt;"",R3&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>126</v>
-      </c>
+      <c r="D4" s="13"/>
       <c r="E4" s="13" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" s="13"/>
+        <v>133</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>134</v>
+      </c>
       <c r="I4" s="13"/>
-      <c r="J4" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J4" s="13"/>
       <c r="K4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L4" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="13"/>
       <c r="M4" s="13"/>
-      <c r="N4" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="14" t="n">
+      <c r="N4" s="13"/>
+      <c r="O4" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A4)</f>
         <v>3</v>
       </c>
-      <c r="Q4" s="14" t="n">
+      <c r="R4" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A4,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R4" s="15" t="str">
-        <f aca="false">IF(AND(D4&lt;&gt;"",F4&lt;&gt;"",G4&lt;&gt;"",Q4&gt;=1),"Yes","Not yet")</f>
+      <c r="S4" s="15" t="str">
+        <f aca="false">IF(AND(E4&lt;&gt;"",G4&lt;&gt;"",H4&lt;&gt;"",R4&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>131</v>
-      </c>
+      <c r="D5" s="13"/>
       <c r="E5" s="13" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="13"/>
+        <v>139</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>140</v>
+      </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J5" s="13"/>
       <c r="K5" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="13"/>
       <c r="M5" s="13"/>
-      <c r="N5" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="14" t="n">
+      <c r="N5" s="13"/>
+      <c r="O5" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A5)</f>
         <v>4</v>
       </c>
-      <c r="Q5" s="14" t="n">
+      <c r="R5" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A5,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R5" s="15" t="str">
-        <f aca="false">IF(AND(D5&lt;&gt;"",F5&lt;&gt;"",G5&lt;&gt;"",Q5&gt;=1),"Yes","Not yet")</f>
+      <c r="S5" s="15" t="str">
+        <f aca="false">IF(AND(E5&lt;&gt;"",G5&lt;&gt;"",H5&lt;&gt;"",R5&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>137</v>
-      </c>
+      <c r="D6" s="13"/>
       <c r="E6" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" s="13"/>
+        <v>145</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>146</v>
+      </c>
       <c r="I6" s="13"/>
-      <c r="J6" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J6" s="13"/>
       <c r="K6" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="13"/>
       <c r="M6" s="13"/>
-      <c r="N6" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="O6" s="13"/>
-      <c r="P6" s="14" t="n">
+      <c r="N6" s="13"/>
+      <c r="O6" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A6)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="14" t="n">
+      <c r="R6" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A6,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R6" s="15" t="str">
-        <f aca="false">IF(AND(D6&lt;&gt;"",F6&lt;&gt;"",G6&lt;&gt;"",Q6&gt;=1),"Yes","Not yet")</f>
+      <c r="S6" s="15" t="str">
+        <f aca="false">IF(AND(E6&lt;&gt;"",G6&lt;&gt;"",H6&lt;&gt;"",R6&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>143</v>
-      </c>
+      <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H7" s="13"/>
+        <v>151</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>152</v>
+      </c>
       <c r="I7" s="13"/>
-      <c r="J7" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J7" s="13"/>
       <c r="K7" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="13"/>
       <c r="M7" s="13"/>
-      <c r="N7" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="14" t="n">
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A7)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="14" t="n">
+      <c r="R7" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A7,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R7" s="15" t="str">
-        <f aca="false">IF(AND(D7&lt;&gt;"",F7&lt;&gt;"",G7&lt;&gt;"",Q7&gt;=1),"Yes","Not yet")</f>
+      <c r="S7" s="15" t="str">
+        <f aca="false">IF(AND(E7&lt;&gt;"",G7&lt;&gt;"",H7&lt;&gt;"",R7&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>149</v>
-      </c>
+      <c r="D8" s="13"/>
       <c r="E8" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="H8" s="13"/>
+        <v>157</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>158</v>
+      </c>
       <c r="I8" s="13"/>
-      <c r="J8" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J8" s="13"/>
       <c r="K8" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="13"/>
       <c r="M8" s="13"/>
-      <c r="N8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="14" t="n">
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A8)</f>
         <v>3</v>
       </c>
-      <c r="Q8" s="14" t="n">
+      <c r="R8" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A8,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R8" s="15" t="str">
-        <f aca="false">IF(AND(D8&lt;&gt;"",F8&lt;&gt;"",G8&lt;&gt;"",Q8&gt;=1),"Yes","Not yet")</f>
+      <c r="S8" s="15" t="str">
+        <f aca="false">IF(AND(E8&lt;&gt;"",G8&lt;&gt;"",H8&lt;&gt;"",R8&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>155</v>
-      </c>
+      <c r="D9" s="13"/>
       <c r="E9" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="13"/>
+        <v>162</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J9" s="13"/>
       <c r="K9" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="13"/>
       <c r="M9" s="13"/>
-      <c r="N9" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="O9" s="13"/>
-      <c r="P9" s="14" t="n">
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A9)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="14" t="n">
+      <c r="R9" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A9,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R9" s="15" t="str">
-        <f aca="false">IF(AND(D9&lt;&gt;"",F9&lt;&gt;"",G9&lt;&gt;"",Q9&gt;=1),"Yes","Not yet")</f>
+      <c r="S9" s="15" t="str">
+        <f aca="false">IF(AND(E9&lt;&gt;"",G9&lt;&gt;"",H9&lt;&gt;"",R9&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="D10" s="13"/>
       <c r="E10" s="13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="H10" s="13"/>
+        <v>168</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="I10" s="13"/>
-      <c r="J10" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J10" s="13"/>
       <c r="K10" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L10" s="13"/>
       <c r="M10" s="13"/>
-      <c r="N10" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="14" t="n">
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A10)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="14" t="n">
+      <c r="R10" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A10,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R10" s="15" t="str">
-        <f aca="false">IF(AND(D10&lt;&gt;"",F10&lt;&gt;"",G10&lt;&gt;"",Q10&gt;=1),"Yes","Not yet")</f>
+      <c r="S10" s="15" t="str">
+        <f aca="false">IF(AND(E10&lt;&gt;"",G10&lt;&gt;"",H10&lt;&gt;"",R10&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>167</v>
-      </c>
+      <c r="D11" s="13"/>
       <c r="E11" s="13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" s="13"/>
+        <v>174</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>175</v>
+      </c>
       <c r="I11" s="13"/>
-      <c r="J11" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J11" s="13"/>
       <c r="K11" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L11" s="13"/>
       <c r="M11" s="13"/>
-      <c r="N11" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="14" t="n">
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A11)</f>
         <v>1</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="R11" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A11,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R11" s="15" t="str">
-        <f aca="false">IF(AND(D11&lt;&gt;"",F11&lt;&gt;"",G11&lt;&gt;"",Q11&gt;=1),"Yes","Not yet")</f>
+      <c r="S11" s="15" t="str">
+        <f aca="false">IF(AND(E11&lt;&gt;"",G11&lt;&gt;"",H11&lt;&gt;"",R11&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>173</v>
-      </c>
+      <c r="D12" s="13"/>
       <c r="E12" s="13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="H12" s="13"/>
+        <v>180</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>181</v>
+      </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J12" s="13"/>
       <c r="K12" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L12" s="13"/>
       <c r="M12" s="13"/>
-      <c r="N12" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="O12" s="13"/>
-      <c r="P12" s="14" t="n">
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A12)</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="R12" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A12,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R12" s="15" t="str">
-        <f aca="false">IF(AND(D12&lt;&gt;"",F12&lt;&gt;"",G12&lt;&gt;"",Q12&gt;=1),"Yes","Not yet")</f>
+      <c r="S12" s="15" t="str">
+        <f aca="false">IF(AND(E12&lt;&gt;"",G12&lt;&gt;"",H12&lt;&gt;"",R12&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>179</v>
-      </c>
+      <c r="D13" s="13"/>
       <c r="E13" s="13" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="13"/>
+        <v>186</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>187</v>
+      </c>
       <c r="I13" s="13"/>
-      <c r="J13" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J13" s="13"/>
       <c r="K13" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="13"/>
       <c r="M13" s="13"/>
-      <c r="N13" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="14" t="n">
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A13)</f>
         <v>2</v>
       </c>
-      <c r="Q13" s="14" t="n">
+      <c r="R13" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A13,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R13" s="15" t="str">
-        <f aca="false">IF(AND(D13&lt;&gt;"",F13&lt;&gt;"",G13&lt;&gt;"",Q13&gt;=1),"Yes","Not yet")</f>
+      <c r="S13" s="15" t="str">
+        <f aca="false">IF(AND(E13&lt;&gt;"",G13&lt;&gt;"",H13&lt;&gt;"",R13&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>185</v>
-      </c>
+      <c r="D14" s="13"/>
       <c r="E14" s="13" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="H14" s="13"/>
+        <v>191</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>192</v>
+      </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="13" t="s">
-        <v>188</v>
-      </c>
+      <c r="J14" s="13"/>
       <c r="K14" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="L14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L14" s="13"/>
       <c r="M14" s="13"/>
-      <c r="N14" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="14" t="n">
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A14)</f>
         <v>3</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="R14" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A14,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R14" s="15" t="str">
-        <f aca="false">IF(AND(D14&lt;&gt;"",F14&lt;&gt;"",G14&lt;&gt;"",Q14&gt;=1),"Yes","Not yet")</f>
+      <c r="S14" s="15" t="str">
+        <f aca="false">IF(AND(E14&lt;&gt;"",G14&lt;&gt;"",H14&lt;&gt;"",R14&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>191</v>
-      </c>
+      <c r="D15" s="13"/>
       <c r="E15" s="13" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="G15" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="K15" s="13" t="s">
+      <c r="L15" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="14" t="n">
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A15)</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="14" t="n">
+      <c r="R15" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A15,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R15" s="15" t="str">
-        <f aca="false">IF(AND(D15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"",Q15&gt;=1),"Yes","Not yet")</f>
+      <c r="S15" s="15" t="str">
+        <f aca="false">IF(AND(E15&lt;&gt;"",G15&lt;&gt;"",H15&lt;&gt;"",R15&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>196</v>
-      </c>
+      <c r="D16" s="13"/>
       <c r="E16" s="13" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="H16" s="13"/>
+        <v>202</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>203</v>
+      </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="13" t="s">
-        <v>188</v>
-      </c>
+      <c r="J16" s="13"/>
       <c r="K16" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="L16" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L16" s="13"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="O16" s="13"/>
-      <c r="P16" s="14" t="n">
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A16)</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="14" t="n">
+      <c r="R16" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A16,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R16" s="15" t="str">
-        <f aca="false">IF(AND(D16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"",Q16&gt;=1),"Yes","Not yet")</f>
+      <c r="S16" s="15" t="str">
+        <f aca="false">IF(AND(E16&lt;&gt;"",G16&lt;&gt;"",H16&lt;&gt;"",R16&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>201</v>
-      </c>
+      <c r="D17" s="13"/>
       <c r="E17" s="13" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="H17" s="13"/>
+        <v>207</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I17" s="13"/>
-      <c r="J17" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J17" s="13"/>
       <c r="K17" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="14" t="n">
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A17)</f>
         <v>3</v>
       </c>
-      <c r="Q17" s="14" t="n">
+      <c r="R17" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A17,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R17" s="15" t="str">
-        <f aca="false">IF(AND(D17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"",Q17&gt;=1),"Yes","Not yet")</f>
+      <c r="S17" s="15" t="str">
+        <f aca="false">IF(AND(E17&lt;&gt;"",G17&lt;&gt;"",H17&lt;&gt;"",R17&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>206</v>
-      </c>
+      <c r="D18" s="13"/>
       <c r="E18" s="13" t="s">
-        <v>114</v>
+        <v>211</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>207</v>
+        <v>120</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="H18" s="13"/>
+        <v>212</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>213</v>
+      </c>
       <c r="I18" s="13"/>
-      <c r="J18" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J18" s="13"/>
       <c r="K18" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="O18" s="13"/>
-      <c r="P18" s="14" t="n">
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A18)</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="R18" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A18,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R18" s="15" t="str">
-        <f aca="false">IF(AND(D18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"",Q18&gt;=1),"Yes","Not yet")</f>
+      <c r="S18" s="15" t="str">
+        <f aca="false">IF(AND(E18&lt;&gt;"",G18&lt;&gt;"",H18&lt;&gt;"",R18&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>211</v>
-      </c>
+      <c r="D19" s="13"/>
       <c r="E19" s="13" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="H19" s="13"/>
+        <v>217</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>218</v>
+      </c>
       <c r="I19" s="13"/>
-      <c r="J19" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J19" s="13"/>
       <c r="K19" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L19" s="13"/>
       <c r="M19" s="13"/>
-      <c r="N19" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="O19" s="13"/>
-      <c r="P19" s="14" t="n">
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A19)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="14" t="n">
+      <c r="R19" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A19,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R19" s="15" t="str">
-        <f aca="false">IF(AND(D19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"",Q19&gt;=1),"Yes","Not yet")</f>
+      <c r="S19" s="15" t="str">
+        <f aca="false">IF(AND(E19&lt;&gt;"",G19&lt;&gt;"",H19&lt;&gt;"",R19&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>216</v>
-      </c>
+      <c r="D20" s="13"/>
       <c r="E20" s="13" t="s">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>217</v>
+        <v>150</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="H20" s="13"/>
+        <v>222</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>223</v>
+      </c>
       <c r="I20" s="13"/>
-      <c r="J20" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J20" s="13"/>
       <c r="K20" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L20" s="13"/>
       <c r="M20" s="13"/>
-      <c r="N20" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="O20" s="13"/>
-      <c r="P20" s="14" t="n">
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A20)</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="14" t="n">
+      <c r="R20" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A20,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R20" s="15" t="str">
-        <f aca="false">IF(AND(D20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"",Q20&gt;=1),"Yes","Not yet")</f>
+      <c r="S20" s="15" t="str">
+        <f aca="false">IF(AND(E20&lt;&gt;"",G20&lt;&gt;"",H20&lt;&gt;"",R20&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>221</v>
-      </c>
+      <c r="D21" s="13"/>
       <c r="E21" s="13" t="s">
-        <v>162</v>
+        <v>226</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="H21" s="13"/>
+        <v>227</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>228</v>
+      </c>
       <c r="I21" s="13"/>
-      <c r="J21" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L21" s="13"/>
       <c r="M21" s="13"/>
-      <c r="N21" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="O21" s="13"/>
-      <c r="P21" s="14" t="n">
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A21)</f>
         <v>3</v>
       </c>
-      <c r="Q21" s="14" t="n">
+      <c r="R21" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A21,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R21" s="15" t="str">
-        <f aca="false">IF(AND(D21&lt;&gt;"",F21&lt;&gt;"",G21&lt;&gt;"",Q21&gt;=1),"Yes","Not yet")</f>
+      <c r="S21" s="15" t="str">
+        <f aca="false">IF(AND(E21&lt;&gt;"",G21&lt;&gt;"",H21&lt;&gt;"",R21&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>226</v>
-      </c>
+      <c r="D22" s="13"/>
       <c r="E22" s="13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="H22" s="13"/>
+        <v>233</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>234</v>
+      </c>
       <c r="I22" s="13"/>
-      <c r="J22" s="13" t="s">
-        <v>117</v>
-      </c>
+      <c r="J22" s="13"/>
       <c r="K22" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L22" s="13"/>
       <c r="M22" s="13"/>
-      <c r="N22" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="O22" s="13"/>
-      <c r="P22" s="14" t="n">
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="14" t="n">
         <f aca="false">COUNTIF(Sources!$B:$B,A22)</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="14" t="n">
+      <c r="R22" s="14" t="n">
         <f aca="false">COUNTIFS(Sources!$B:$B,A22,Sources!$J:$J,"yes")</f>
         <v>0</v>
       </c>
-      <c r="R22" s="15" t="str">
-        <f aca="false">IF(AND(D22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"",Q22&gt;=1),"Yes","Not yet")</f>
+      <c r="S22" s="15" t="str">
+        <f aca="false">IF(AND(E22&lt;&gt;"",G22&lt;&gt;"",H22&lt;&gt;"",R22&gt;=1),"Yes","Not yet")</f>
         <v>Not yet</v>
       </c>
     </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A23)</f>
+        <v>2</v>
+      </c>
+      <c r="R23" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A23,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="15" t="str">
+        <f aca="false">IF(AND(E23&lt;&gt;"",G23&lt;&gt;"",H23&lt;&gt;"",R23&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A24)</f>
+        <v>1</v>
+      </c>
+      <c r="R24" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A24,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="15" t="str">
+        <f aca="false">IF(AND(E24&lt;&gt;"",G24&lt;&gt;"",H24&lt;&gt;"",R24&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A25)</f>
+        <v>2</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A25,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="15" t="str">
+        <f aca="false">IF(AND(E25&lt;&gt;"",G25&lt;&gt;"",H25&lt;&gt;"",R25&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A26)</f>
+        <v>1</v>
+      </c>
+      <c r="R26" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A26,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="15" t="str">
+        <f aca="false">IF(AND(E26&lt;&gt;"",G26&lt;&gt;"",H26&lt;&gt;"",R26&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A27)</f>
+        <v>2</v>
+      </c>
+      <c r="R27" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A27,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="15" t="str">
+        <f aca="false">IF(AND(E27&lt;&gt;"",G27&lt;&gt;"",H27&lt;&gt;"",R27&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A28)</f>
+        <v>1</v>
+      </c>
+      <c r="R28" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A28,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="15" t="str">
+        <f aca="false">IF(AND(E28&lt;&gt;"",G28&lt;&gt;"",H28&lt;&gt;"",R28&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A29)</f>
+        <v>1</v>
+      </c>
+      <c r="R29" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A29,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="15" t="str">
+        <f aca="false">IF(AND(E29&lt;&gt;"",G29&lt;&gt;"",H29&lt;&gt;"",R29&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A30)</f>
+        <v>1</v>
+      </c>
+      <c r="R30" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A30,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="15" t="str">
+        <f aca="false">IF(AND(E30&lt;&gt;"",G30&lt;&gt;"",H30&lt;&gt;"",R30&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A31)</f>
+        <v>1</v>
+      </c>
+      <c r="R31" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A31,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="15" t="str">
+        <f aca="false">IF(AND(E31&lt;&gt;"",G31&lt;&gt;"",H31&lt;&gt;"",R31&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="14" t="n">
+        <f aca="false">COUNTIF(Sources!$B:$B,A32)</f>
+        <v>2</v>
+      </c>
+      <c r="R32" s="14" t="n">
+        <f aca="false">COUNTIFS(Sources!$B:$B,A32,Sources!$J:$J,"yes")</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="15" t="str">
+        <f aca="false">IF(AND(E32&lt;&gt;"",G32&lt;&gt;"",H32&lt;&gt;"",R32&gt;=1),"Yes","Not yet")</f>
+        <v>Not yet</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R22"/>
-  <conditionalFormatting sqref="D2:D300">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>LEN(D2)-LEN(SUBSTITUTE(D2," ",""))+1&gt;10</formula>
+  <autoFilter ref="A1:S32"/>
+  <conditionalFormatting sqref="E2:E300">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>LEN(E2)-LEN(SUBSTITUTE(E2," ",""))+1&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G300">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>LEN(G2)-LEN(SUBSTITUTE(G2," ",""))+1&gt;25</formula>
+  <conditionalFormatting sqref="H2:H300">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>LEN(H2)-LEN(SUBSTITUTE(H2," ",""))+1&gt;25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K300">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>AND(K2="live",Q2&lt;1)</formula>
+  <conditionalFormatting sqref="L2:L300">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>AND(L2="live",R2&lt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R300">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>R2="Yes"</formula>
+  <conditionalFormatting sqref="S2:S300">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>S2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -4271,15 +5236,15 @@
       <formula1>Topics!$A$2:$A$40</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E300" type="list">
+    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F300" type="list">
       <formula1>Lists!$C$2:$C$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J300" type="list">
+    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K300" type="list">
       <formula1>Lists!$E$2:$E$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K300" type="list">
+    <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L300" type="list">
       <formula1>Lists!$A$2:$A$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4301,7 +5266,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -4321,72 +5286,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="J1" s="12" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>241</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>243</v>
+        <v>304</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>244</v>
+        <v>305</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>246</v>
+        <v>307</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
@@ -4398,26 +5363,26 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
       <c r="J3" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
@@ -4429,26 +5394,26 @@
     </row>
     <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>251</v>
+        <v>312</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>252</v>
+        <v>313</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
@@ -4460,26 +5425,26 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
@@ -4491,26 +5456,26 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
@@ -4522,26 +5487,26 @@
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
       <c r="J7" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
@@ -4553,26 +5518,26 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>267</v>
+        <v>328</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
@@ -4584,26 +5549,26 @@
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="13" t="s">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
@@ -4615,26 +5580,26 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>275</v>
+        <v>336</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="s">
-        <v>277</v>
+        <v>338</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
@@ -4646,26 +5611,26 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
@@ -4677,26 +5642,26 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="13" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
@@ -4708,26 +5673,26 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>287</v>
+        <v>348</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="13" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
@@ -4739,26 +5704,26 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="13" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
@@ -4770,28 +5735,28 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>297</v>
+        <v>358</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>298</v>
+        <v>359</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
@@ -4803,26 +5768,26 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>299</v>
+        <v>360</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="13" t="s">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
@@ -4834,26 +5799,26 @@
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="13" t="s">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
@@ -4865,26 +5830,26 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="13" t="s">
-        <v>310</v>
+        <v>371</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
@@ -4896,26 +5861,26 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>311</v>
+        <v>372</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>313</v>
+        <v>374</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="13" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
@@ -4927,26 +5892,26 @@
     </row>
     <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
@@ -4958,26 +5923,26 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>319</v>
+        <v>380</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>320</v>
+        <v>381</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="13" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
@@ -4989,26 +5954,26 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>322</v>
+        <v>383</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>324</v>
+        <v>385</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13" t="s">
-        <v>325</v>
+        <v>386</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
       <c r="J22" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
@@ -5020,26 +5985,26 @@
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>326</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>265</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
       <c r="J23" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
@@ -5049,10 +6014,552 @@
         <v>OK</v>
       </c>
     </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B24)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B25)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B26)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B27)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B28)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B29)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B30)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B31)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B32)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B33)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B34)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B35)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B36)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="15" t="str">
+        <f aca="false">IF(COUNTIF(Facts!$A:$A,B37)=0,"Fact id not found","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N23"/>
+  <autoFilter ref="A1:N37"/>
   <conditionalFormatting sqref="N2:N300">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>N2&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5091,7 +6598,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -5109,54 +6616,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>329</v>
+        <v>453</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>330</v>
+        <v>454</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>331</v>
+        <v>455</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>332</v>
+        <v>456</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>333</v>
+        <v>457</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>334</v>
+        <v>458</v>
       </c>
       <c r="B2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>335</v>
+        <v>459</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>336</v>
+        <v>460</v>
       </c>
       <c r="E2" s="13" t="n">
         <v>-4</v>
@@ -5165,10 +6672,10 @@
         <v>-1</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>41</v>
@@ -5182,16 +6689,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>337</v>
+        <v>461</v>
       </c>
       <c r="B3" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>338</v>
+        <v>462</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>0</v>
@@ -5200,10 +6707,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>41</v>
@@ -5217,16 +6724,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>339</v>
+        <v>463</v>
       </c>
       <c r="B4" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>340</v>
+        <v>464</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>341</v>
+        <v>465</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>0</v>
@@ -5235,17 +6742,17 @@
         <v>1</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I4" s="13" t="s">
         <v>41</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13" t="s">
-        <v>342</v>
+        <v>466</v>
       </c>
       <c r="L4" s="15" t="str">
         <f aca="false">IF(F4&lt;E4,"Check: ends before it starts",IF(AND(G4&lt;&gt;"",COUNTIF(Facts!$A:$A,G4)=0),"Fact id not found","OK"))</f>
@@ -5254,16 +6761,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>343</v>
+        <v>467</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>344</v>
+        <v>468</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>1</v>
@@ -5272,10 +6779,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>41</v>
@@ -5289,16 +6796,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>346</v>
+        <v>470</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>347</v>
+        <v>471</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>348</v>
+        <v>472</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>2</v>
@@ -5308,7 +6815,7 @@
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>41</v>
@@ -5322,16 +6829,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>349</v>
+        <v>473</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>351</v>
+        <v>475</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>3</v>
@@ -5340,10 +6847,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>41</v>
@@ -5357,16 +6864,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>352</v>
+        <v>476</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>353</v>
+        <v>477</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>354</v>
+        <v>478</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>6</v>
@@ -5376,7 +6883,7 @@
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>41</v>
@@ -5388,18 +6895,18 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>355</v>
+        <v>479</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>356</v>
+        <v>480</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>357</v>
+        <v>481</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>17</v>
@@ -5407,9 +6914,11 @@
       <c r="F9" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>243</v>
+      </c>
       <c r="H9" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>41</v>
@@ -5423,28 +6932,28 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>358</v>
+        <v>482</v>
       </c>
       <c r="B10" s="13" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>359</v>
+        <v>483</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>41</v>
@@ -5456,10 +6965,45 @@
         <v>OK</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="15" t="str">
+        <f aca="false">IF(F11&lt;E11,"Check: ends before it starts",IF(AND(G11&lt;&gt;"",COUNTIF(Facts!$A:$A,G11)=0),"Fact id not found","OK"))</f>
+        <v>OK</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:L11"/>
   <conditionalFormatting sqref="L2:L300">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>L2&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5498,7 +7042,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -5516,137 +7060,167 @@
         <v>65</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>361</v>
+        <v>488</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>362</v>
+        <v>489</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>363</v>
+        <v>490</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>364</v>
+        <v>491</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>365</v>
+        <v>492</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>366</v>
+        <v>493</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>367</v>
+        <v>494</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>368</v>
+        <v>495</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>369</v>
+        <v>496</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>370</v>
+        <v>497</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" s="13"/>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E11"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Pick a value from the dropdown. To add a new option, add it on the Lists tab." errorStyle="stop" errorTitle="Not in the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A300" type="list">
       <formula1>Topics!$A$2:$A$40</formula1>
@@ -5682,25 +7256,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>371</v>
+        <v>500</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>372</v>
+        <v>501</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5708,22 +7282,22 @@
         <v>41</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>74</v>
-      </c>
       <c r="E2" s="17" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5731,22 +7305,22 @@
         <v>43</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>375</v>
+        <v>502</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>376</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5754,19 +7328,19 @@
         <v>45</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>377</v>
+        <v>504</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>379</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5774,108 +7348,108 @@
         <v>47</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>381</v>
+        <v>506</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="17" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>383</v>
+        <v>507</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>384</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>385</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="17" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>386</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>387</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="17" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="17" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="17" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="17" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="17" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="17" t="s">
-        <v>388</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="17" t="s">
-        <v>389</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="17" t="s">
-        <v>390</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="17" t="s">
-        <v>391</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
